--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB6FFC5-5DCD-4C8F-94DB-03B026D9824D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD3E071-5810-45C8-BA0E-C91EB3CF17B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="3060" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="47">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -45,152 +45,165 @@
     <t>Name</t>
   </si>
   <si>
+    <t>한글 이름</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>창 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>창을 이용해 적을 찌르는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tower</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하늘을 날아다니는 몬스터. 특정 기물들만 공격을 할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconPath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도끼 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_04</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_06</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독침 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>밧줄 원시인</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_04</t>
+  </si>
+  <si>
+    <t>enemy_05</t>
+  </si>
+  <si>
+    <t>케찰코아틀루스</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>검치호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>매머드</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도끼를 이용해 적을 공격하는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Sprite/Icon/ChickenIcon.png</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Sprite/Icon/Pig.png</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 적</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체력이 많은 적 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>한글 이름</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>창 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>창을 이용해 적을 찌르는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>닭</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돼지</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>E</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>EntityType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tower</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>하늘을 날아다니는 몬스터. 특정 기물들만 공격을 할 수 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>IconPath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도끼 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_04</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_05</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>tower_06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>화살 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>독침 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>밧줄 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_04</t>
-  </si>
-  <si>
-    <t>enemy_05</t>
-  </si>
-  <si>
-    <t>케찰코아틀루스</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>검치호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>매머드</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도끼를 이용해 적을 공격하는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Sprite/Icon/ChickenIcon.png</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Sprite/Icon/Pig.png</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 적</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">체력이 많은 적 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ss</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddd</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dddas</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -198,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -243,6 +256,20 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -333,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -368,6 +395,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -603,13 +634,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -630,10 +661,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="8"/>
@@ -649,14 +680,14 @@
       <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>24</v>
+      <c r="C3" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>23</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -667,19 +698,19 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>9</v>
-      </c>
       <c r="D4" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
@@ -694,19 +725,19 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -721,17 +752,19 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="D6" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -746,17 +779,19 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="13"/>
+        <v>30</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="D7" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -771,17 +806,19 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="13"/>
+        <v>31</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="D8" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -796,17 +833,19 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="D9" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -821,19 +860,19 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -848,19 +887,19 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>19</v>
-      </c>
       <c r="E11" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -875,19 +914,19 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>22</v>
-      </c>
       <c r="D12" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -902,17 +941,19 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="D13" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -927,17 +968,19 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="18"/>
+        <v>37</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>46</v>
+      </c>
       <c r="D14" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD3E071-5810-45C8-BA0E-C91EB3CF17B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62245A7E-ACD9-4DE4-90A7-16C03D7C00B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -175,14 +175,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Sprite/Icon/ChickenIcon.png</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Sprite/Icon/Pig.png</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>기본 적</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -204,6 +196,25 @@
   </si>
   <si>
     <t>dddas</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_01_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_02_icon</t>
+  </si>
+  <si>
+    <t>Sprite/Icon/ChickenIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Sprite/Icon/ChickenIcon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Sprite/Icon/Pig</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -681,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>12</v>
@@ -710,7 +721,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
@@ -737,7 +748,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -758,13 +769,13 @@
         <v>26</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -785,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -812,13 +823,13 @@
         <v>31</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -839,13 +850,13 @@
         <v>32</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -866,13 +877,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -893,13 +904,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -926,7 +937,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -947,13 +958,13 @@
         <v>36</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -974,13 +985,13 @@
         <v>37</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62245A7E-ACD9-4DE4-90A7-16C03D7C00B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B23A50-1F24-4DED-8991-B1ECA671FAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29235" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -215,6 +215,10 @@
   </si>
   <si>
     <t>Assets/Sprite/Icon/Pig</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_03_icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -775,7 +779,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B23A50-1F24-4DED-8991-B1ECA671FAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3F49BF-34ED-47DE-BE9B-B7EA06D69585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29235" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -219,6 +219,10 @@
   </si>
   <si>
     <t>Sprite/Icon/tower_03_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_04_icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -806,7 +810,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3F49BF-34ED-47DE-BE9B-B7EA06D69585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E1C48C-3A7A-4240-BEDA-8C95A69926D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29235" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -206,10 +206,6 @@
     <t>Sprite/Icon/tower_02_icon</t>
   </si>
   <si>
-    <t>Sprite/Icon/ChickenIcon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Sprite/Icon/ChickenIcon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -223,6 +219,14 @@
   </si>
   <si>
     <t>Sprite/Icon/tower_04_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_05_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/tower_06_icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -783,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -810,7 +814,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -837,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -864,7 +868,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -891,7 +895,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -918,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -945,7 +949,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -972,7 +976,7 @@
         <v>18</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -999,7 +1003,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E1C48C-3A7A-4240-BEDA-8C95A69926D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29235" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E1C48C-3A7A-4240-BEDA-8C95A69926D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F7DF8D-5F53-41EE-8C38-5FAE14EC6B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F7DF8D-5F53-41EE-8C38-5FAE14EC6B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD49A0B-6ADD-488D-B8D2-9E49F7749E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -53,10 +53,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>창을 이용해 적을 찌르는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>닭</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -171,10 +167,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>도끼를 이용해 적을 공격하는 원시인. 날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>기본 적</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -187,10 +179,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ss</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>ddd</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -227,6 +215,30 @@
   </si>
   <si>
     <t>Sprite/Icon/tower_06_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독침을 이용해 적의 방어력을 감소시키는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>창을 이용해 적을 찌르는 원시인\n날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도끼를 이용해 적을 공격하는 원시인\n날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌을 던져 먼 거리에서 공격할 수 있는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살을 이용해 먼 거리를 강력하게 공격할 수 있는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>밧줄을 던져 적의 이동속도를 감소시키는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -645,7 +657,7 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="78.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="34.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
@@ -663,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -684,10 +696,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="8"/>
@@ -704,13 +716,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -721,19 +733,19 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
@@ -748,19 +760,19 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -775,19 +787,19 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -802,19 +814,19 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -829,19 +841,19 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -856,19 +868,19 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -883,19 +895,19 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -910,19 +922,19 @@
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="E11" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
@@ -937,19 +949,19 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>21</v>
-      </c>
       <c r="D12" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -964,19 +976,19 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -991,19 +1003,19 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>

--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD49A0B-6ADD-488D-B8D2-9E49F7749E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86166028-B2C1-49D3-A752-71E894D51953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,27 +218,27 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>독침을 이용해 적의 방어력을 감소시키는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>창을 이용해 적을 찌르는 원시인\n날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>도끼를 이용해 적을 공격하는 원시인\n날아다니는 유닛을 공격할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌을 던져 먼 거리에서 공격할 수 있는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>화살을 이용해 먼 거리를 강력하게 공격할 수 있는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>밧줄을 던져 적의 이동속도를 감소시키는 원시인\n지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <t>창을 이용해 적을 찌르는 원시인&lt;br&gt;날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>도끼를 이용해 적을 공격하는 원시인&lt;br&gt;날아다니는 유닛을 공격할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌을 던져 먼 거리에서 공격할 수 있는 원시인&lt;br&gt;지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살을 이용해 먼 거리를 강력하게 공격할 수 있는 원시인&lt;br&gt;지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>독침을 이용해 적의 방어력을 감소시키는 원시인&lt;br&gt;지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>밧줄을 던져 적의 이동속도를 감소시키는 원시인&lt;br&gt;지상과 공중 유닛을 공격할 수 있습니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -395,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -434,6 +434,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -738,8 +741,8 @@
       <c r="B4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>51</v>
+      <c r="C4" s="22" t="s">
+        <v>50</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
@@ -766,7 +769,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
@@ -793,7 +796,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
@@ -820,7 +823,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
@@ -847,7 +850,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
